--- a/outputs/evaluation/architecture/validation/CF_M04/run_2/CF_M04_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_2/CF_M04_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AI service used for generating response suggestions.</t>
+          <t>AI service integrated for generating review responses.</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>The backend follows the Hexagonal Architecture (Ports and Adapters) pattern, which allows separating business logic from the framework and infrastructure technologies.</t>
+          <t>The back-end follows the Hexagonal Architecture pattern (Ports and Adapters), which allows separating business logic from the framework and infrastructure technologies.</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -961,7 +961,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>The backend follows the Hexagonal Architecture (Ports and Adapters) pattern, which allows separating business logic from the framework and infrastructure technologies.</t>
+          <t>The back-end follows the Hexagonal Architecture pattern (Ports and Adapters), which allows separating business logic from the framework and infrastructure technologies.</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -971,12 +971,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M04_P04</t>
+          <t>CF_M04_P07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bloc/Cubit</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -986,82 +986,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>For state and business logic management, the Bloc pattern is used, specificallythrough its Cubit variant, widely used in Flutter applications modern.</t>
+          <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_M04_AU01</t>
+          <t>CF_M04_AU04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Hexagonal Architecture</t>
-        </is>
-      </c>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>The backend follows the Hexagonal Architecture (Ports and Adapters) pattern, which allows separating business logic from the framework and infrastructure technologies.</t>
+          <t>The back-end interacts with the database using the Django ORM.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.6284999999999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M04_P07</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>66</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CF_M04_AU04</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>El back-end està implementat utilitzant Django i segueix el patró d’Arquitectura Hexagonal [...] La persistència de les dades es realitza mitjançant una base de dades relacional MySQL, gestionada a través de l’ORM de Django.</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0.696</v>
+        <v>0.7403999999999999</v>
       </c>
     </row>
   </sheetData>
